--- a/outputs/식이_최종반영_20260922/이전본_보관/버전통일전/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/식이_최종반영_20260922/이전본_보관/버전통일전/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Rdfd264ff458f4484"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문구세트" sheetId="2" r:id="R2dff96e9076b4977"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="축정의" sheetId="3" r:id="Re145b3a3e28c4ad8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드매핑" sheetId="4" r:id="R30401622b698458e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정값" sheetId="5" r:id="R56afad6327674340"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Rb7c3967185ba4b41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문구세트" sheetId="2" r:id="Rce7b8c3862ce4a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="축정의" sheetId="3" r:id="Rb6701f5ab3f84971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드매핑" sheetId="4" r:id="R882dd663fbcc41fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정값" sheetId="5" r:id="R84756fd3205d4c50"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -526,7 +526,6 @@
         <x:v>163개 운영 문구·문구 ID·전문의 승인 필드</x:v>
       </x:c>
       <x:c r="C5" s="18" t="n">
-        <x:f>COUNTA(문구세트!G2:G164)</x:f>
         <x:v>163</x:v>
       </x:c>
     </x:row>
@@ -538,7 +537,6 @@
         <x:v>8축 · 회전 문항 · 답 3개</x:v>
       </x:c>
       <x:c r="C6" s="18" t="n">
-        <x:f>COUNTA(축정의!B2:B100)</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -550,7 +548,6 @@
         <x:v>질환별 연결 축 · 금지 문구 (검수 7건 반영)</x:v>
       </x:c>
       <x:c r="C7" s="18" t="n">
-        <x:f>COUNTA(상병코드매핑!B2:B100)</x:f>
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -562,7 +559,6 @@
         <x:v>경계 · 창 · 시각 · 폭 · 스위치 · 임의값</x:v>
       </x:c>
       <x:c r="C8" s="18" t="n">
-        <x:f>COUNTA(설정값!B2:B100)</x:f>
         <x:v>52</x:v>
       </x:c>
     </x:row>
@@ -586,7 +582,6 @@
         <x:v>기획 후보. 전문의 승인 후 개인 조건 필터를 통과해야 노출</x:v>
       </x:c>
       <x:c r="C11" s="18" t="n">
-        <x:f>COUNTIF(문구세트!C2:C164,"사용")</x:f>
         <x:v>163</x:v>
       </x:c>
     </x:row>
